--- a/word-list/German.xlsx
+++ b/word-list/German.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\word-list 2026-04-20\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D333641-122C-4562-83E3-B34E0D237F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C507241C-5CF6-44E2-92CB-61DB98DB44F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{8BD51AC8-827B-4722-9D7F-2820016BFAAB}"/>
+    <workbookView xWindow="16466" yWindow="5040" windowWidth="15600" windowHeight="11331" xr2:uid="{8BD51AC8-827B-4722-9D7F-2820016BFAAB}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-German" sheetId="1" r:id="rId1"/>
@@ -99,9 +99,6 @@
     <t>Frage</t>
   </si>
   <si>
-    <t>gut</t>
-  </si>
-  <si>
     <t>heute</t>
   </si>
   <si>
@@ -162,9 +159,6 @@
     <t>aus</t>
   </si>
   <si>
-    <t>Tag</t>
-  </si>
-  <si>
     <t>finden</t>
   </si>
   <si>
@@ -334,6 +328,12 @@
   </si>
   <si>
     <t>Unterschied</t>
+  </si>
+  <si>
+    <t>Straße</t>
+  </si>
+  <si>
+    <t>Stelle</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1403,7 @@
         <v>20</v>
       </c>
       <c r="C19">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
@@ -1444,7 +1444,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C23">
         <v>0.6</v>
@@ -1455,7 +1455,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>0.6</v>
@@ -1466,7 +1466,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>0.6</v>
@@ -1477,7 +1477,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>0.3</v>
@@ -1488,7 +1488,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>0.6</v>
@@ -1499,7 +1499,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28">
         <v>0.6</v>
@@ -1510,7 +1510,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <v>0.6</v>
@@ -1521,7 +1521,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1532,7 +1532,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <v>0.6</v>
@@ -1543,7 +1543,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <v>0.6</v>
@@ -1554,7 +1554,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33">
         <v>0.6</v>
@@ -1565,7 +1565,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1576,7 +1576,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35">
         <v>0.6</v>
@@ -1587,7 +1587,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36">
         <v>0.6</v>
@@ -1598,7 +1598,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37">
         <v>0.6</v>
@@ -1609,7 +1609,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1620,7 +1620,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <v>0.6</v>
@@ -1631,7 +1631,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C40">
         <v>0.6</v>
@@ -1642,10 +1642,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
@@ -1653,7 +1653,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42">
         <v>0.3</v>
@@ -1664,7 +1664,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1675,7 +1675,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C44">
         <v>0.6</v>
@@ -1686,10 +1686,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
@@ -1697,7 +1697,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1708,7 +1708,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C47">
         <v>0.6</v>
@@ -1719,10 +1719,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C48">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
@@ -1730,7 +1730,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1741,7 +1741,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C50">
         <v>0.6</v>
@@ -1752,7 +1752,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51">
         <v>0.3</v>
@@ -1763,7 +1763,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C53">
         <v>0.6</v>
@@ -1785,10 +1785,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C54">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
@@ -1796,7 +1796,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1807,7 +1807,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C56">
         <v>0.6</v>
@@ -1818,7 +1818,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C57">
         <v>0.3</v>
@@ -1829,7 +1829,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1840,7 +1840,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C59">
         <v>0.6</v>
@@ -1851,10 +1851,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C60">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
@@ -1862,7 +1862,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1873,7 +1873,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C62">
         <v>0.6</v>
@@ -1884,7 +1884,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C63">
         <v>0.3</v>
@@ -1895,7 +1895,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1906,7 +1906,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C65">
         <v>0.6</v>
@@ -1917,7 +1917,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C66">
         <v>0.3</v>
@@ -1928,7 +1928,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -1939,7 +1939,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C68">
         <v>0.6</v>
@@ -1950,7 +1950,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C69">
         <v>0.3</v>
@@ -1961,7 +1961,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -1972,7 +1972,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C71">
         <v>0.6</v>
@@ -1983,7 +1983,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C72">
         <v>0.3</v>
@@ -1994,7 +1994,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2005,7 +2005,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C74">
         <v>0.6</v>
@@ -2016,7 +2016,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C75">
         <v>0.3</v>
@@ -2027,7 +2027,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -2038,10 +2038,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C77">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.4">
@@ -2049,7 +2049,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C78">
         <v>0.3</v>
@@ -2060,7 +2060,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -2071,7 +2071,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C80">
         <v>0.6</v>
@@ -2082,7 +2082,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C81">
         <v>0.3</v>
@@ -2093,7 +2093,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -2104,7 +2104,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C83">
         <v>0.6</v>
@@ -2115,7 +2115,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C84">
         <v>0.3</v>
@@ -2126,7 +2126,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -2137,7 +2137,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C86">
         <v>0.6</v>
@@ -2148,7 +2148,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C87">
         <v>0.3</v>
@@ -2159,7 +2159,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C89">
         <v>0.6</v>
@@ -2181,7 +2181,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C90">
         <v>0.3</v>
@@ -2192,7 +2192,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -2203,10 +2203,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C92">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.4">
@@ -2214,7 +2214,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C93">
         <v>0.3</v>
@@ -2225,7 +2225,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -2236,7 +2236,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C95">
         <v>0.6</v>
@@ -2247,7 +2247,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C96">
         <v>0.3</v>
@@ -2258,7 +2258,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C97">
         <v>0.1</v>
@@ -2269,7 +2269,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C98">
         <v>0.1</v>
@@ -2280,7 +2280,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C99">
         <v>0.1</v>
@@ -2291,7 +2291,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C100">
         <v>0.1</v>
@@ -2302,7 +2302,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C101">
         <v>0.1</v>
